--- a/쿼리분석/소스프로그램_분석_요약_20260628.xlsx
+++ b/쿼리분석/소스프로그램_분석_요약_20260628.xlsx
@@ -4,18 +4,19 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="840" yWindow="825" windowWidth="19935" windowHeight="7140" activeTab="1"/>
+    <workbookView xWindow="840" yWindow="825" windowWidth="19935" windowHeight="7140" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="소스 프로그램 분석 요약" sheetId="1" r:id="rId1"/>
     <sheet name="0701분석" sheetId="2" r:id="rId2"/>
+    <sheet name="서버리니지추출" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="231">
   <si>
     <t xml:space="preserve">  ■ 소스 프로그램 매개변수 및 주요 기능 분석 요약</t>
   </si>
@@ -854,12 +855,944 @@
       <t xml:space="preserve"> 등)</t>
     </r>
   </si>
+  <si>
+    <t>아래 2개 소스로직 비교 분석 차이 정리요청 D:\workspace\enc\쿼리분석\sql_v12_full_new_02_col.py D:\workspace\enc\쿼리분석\sql_v12_full_new_03_col.py sql_v12_full_new_03_col.py 가 보완이 된 것이 있다면 내용 별도 정리</t>
+  </si>
+  <si>
+    <t>오전 12:34</t>
+  </si>
+  <si>
+    <t>두 소스 코드 </t>
+  </si>
+  <si>
+    <t>sql_v12_full_new_02_col.py와 </t>
+  </si>
+  <si>
+    <t>[분석 보고서] sql_v12_full_new_02_col.py vs 03_col.py 비교 및 보완점</t>
+  </si>
+  <si>
+    <t>1. 핵심 차이점 요약</t>
+  </si>
+  <si>
+    <t>비교 항목</t>
+  </si>
+  <si>
+    <t>sql_v12_full_new_02_col.py</t>
+  </si>
+  <si>
+    <t>sql_v12_full_new_03_col.py</t>
+  </si>
+  <si>
+    <t>미지원 (개념 없음)</t>
+  </si>
+  <si>
+    <t>지원 (대상 디렉토리의 최하위 폴더명 자동 지정)</t>
+  </si>
+  <si>
+    <t>결과 테이블 생성 방식</t>
+  </si>
+  <si>
+    <t>결과 테이블 이름 구조</t>
+  </si>
+  <si>
+    <t>동작 데이터 삭제 단위</t>
+  </si>
+  <si>
+    <t>없음 (테이블 단위 DROP)</t>
+  </si>
+  <si>
+    <t>결과 CSV 헤더 구조</t>
+  </si>
+  <si>
+    <t>동적 테이블 보정</t>
+  </si>
+  <si>
+    <t>없음 (DROP 처리)</t>
+  </si>
+  <si>
+    <t>2. 세부 상세 비교</t>
+  </si>
+  <si>
+    <t>python</t>
+  </si>
+  <si>
+    <t># 03_col.py 추가된 부분 (L1641)</t>
+  </si>
+  <si>
+    <t>② DB 적재 프로세스의 안전성 향상 (DROP &amp; CREATE ➔ DELETE &amp; INSERT)</t>
+  </si>
+  <si>
+    <t>1. 대상 테이블이 존재하는지 확인하고 없으면 신규 생성합니다.</t>
+  </si>
+  <si>
+    <t>③ 데이터 스키마 및 INSERT 쿼리 확장</t>
+  </si>
+  <si>
+    <r>
+      <t>sql_v12_full_new_03_col.py를 정밀 분석한 결과와 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>03_col.py</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>에서 보완된 사항을 정리한 보고서입니다.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>두 프로그램은 SQL 소스 파일들(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.sql</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.hql</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.uld</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.ld</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.sh</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>)을 분석하여 데이터 흐름 리니지 및 검색 컬럼과의 매칭 정보(칼럼 매칭 결과)를 추출하는 파이썬 3 기반 분석 툴입니다. 핵심 로직과 파싱 규칙은 동일하지만, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>결과물 식별과 데이터베이스 적재 정책</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 부분에서 큰 차이가 있습니다.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>mid</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 디렉토리 식별자</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>매 실행 시 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9.9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>DROP</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 후 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9.9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>CREATE</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> (Full-Replace)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>기존 테이블 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>유지 후 재생성 방지 (Incremental)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>p190872_{하위폴더명}_{mode}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> (실행 경로별 분할)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>p190872_all_{mode}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> (하나의 통합 테이블로 관리)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>동일한 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9.9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>mid</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>에 해당하는 데이터만 선별 삭제 (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9.9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>DELETE WHERE mid = %s</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>mid</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 컬럼 없음</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>헤더 첫 번째 컬럼에 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9.9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>mid</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 추가</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>기존 테이블에 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>mid</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 컬럼 누락 시 자동 추가 (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>ALTER TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>① 디렉토리 식별 단위 (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>mid</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.5"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>) 개념 도입</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>03_col.py</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 에서는 소스 디렉토리의 마지막 폴더명을 Module ID(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>mid</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>)로 인식하는 기능이 탑재되었습니다.</t>
+    </r>
+  </si>
+  <si>
+    <t>mid = os.path.basename(os.path.normpath(SOURCE_DIR))</t>
+  </si>
+  <si>
+    <r>
+      <t>이에 따라 결과 CSV 구조(리니지, 칼럼매칭)에 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>mid</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 필드가 첫 번째 헤더로 포함되어, 수집된 결과 행이 어떤 분석 단위(디렉토리)에서 추출된 데이터인지 즉시 역추적할 수 있습니다.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>02_col.py</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 는 데이터 적재 시 무조건 기존 테이블을 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>DROP &amp; CREATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 하므로 테이블당 1개의 디렉토리 결과만 보관할 수 있습니다.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>03_col.py</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 는 테이블을 날리지 않고 다음과 같이 방어적으로 수행합니다.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2. 기존 테이블 스키마에 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>mid</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 컬럼이 없는 구버전 상태일 경우 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>ALTER TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 구문을 수행하여 자동으로 컬럼을 확장해 줍니다.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>3. 현재 검색한 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>mid</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>에 대한 기존 데이터만 선별적으로 삭제(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>DELETE FROM table WHERE mid = %s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>)한 후 데이터를 적재합니다.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>결과적으로 단일 테이블(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9.9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>p190872_all_col_match</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>) 내에서 여러 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9.9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>mid</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 분석 데이터를 충돌 없이 누적 관리할 수 있습니다.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>mid</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 필드 바인딩을 위해 DDL 선언과 INSERT 문에 컬럼 바인딩 개수가 각각 확장되었습니다.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>리니지 적재 쿼리:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 바인딩 파라미터가 16개에서 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>17개</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>로 변경 (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>mid</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 추가)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>쿼리 텍스트 적재 쿼리:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 바인딩 파라미터가 7개에서 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>8개</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>로 변경 (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>mid</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 추가)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>칼럼 매칭 적재 쿼리:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 바인딩 파라미터가 17개에서 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>18개</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>로 변경 (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>mid</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 추가)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>3. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>sql_v12_full_new_03_col.py</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 의 보완 및 강점 요약</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1. 배치 결과의 통합 누적 보관 가능:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 디렉토리가 다르더라도 하나의 통합 DB 테이블(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>p190872_all_...</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>)에 차곡차곡 누적 저장할 수 있어 데이터 관리 효율이 극대화됩니다.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2. 원천 경로 역추적성 강화:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> CSV 결과 및 DB 테이블에 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>mid</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>가 기록되어, 결과값이 어떤 서브 모듈 소스 코드에서 유래한 컬럼인지 구분 분석하기 용이합니다.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>3. 스키마 변경에 유연한 대응:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 기존 테이블에 컬럼이 부족하더라도 배치 중단(에러) 없이 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>ALTER TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> 로 보정하여 비즈니스 배치의 안정성을 향상시켰습니다.</t>
+    </r>
+  </si>
+  <si>
+    <t>D:\workspace\enc\쿼리분석\sql_v12_full_new_03_col.py</t>
+  </si>
+  <si>
+    <t>서버에서리니지추출</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>D:\workspace\enc\쿼리분석\sql_v12_full_new_03_local_col.py</t>
+  </si>
+  <si>
+    <t>D:\workspace\enc\쿼리분석\sql_v12_full_new_02_local_col.py</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>--in 파일명  또는 --col "칼럼명,칼럼명"</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>--in 파일명포함 grep후  and --col "칼럼명,칼럼명"</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>D:\workspace\enc\쿼리분석\p190872_local_chk_v09_gm.py</t>
+  </si>
+  <si>
+    <t>암호화 칼럼 매칭라인 추출 --where new|old|all</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>프로그램</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>설명</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="9">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -915,6 +1848,85 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9.9"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9.9"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9.9"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13.5"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9.9"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -942,7 +1954,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -1017,11 +2029,137 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1044,61 +2182,144 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1106,6 +2327,77 @@
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1025" name="AutoShape 1" descr="vscode-file://vscode-app/c:/Users/user/AppData/Local/Programs/Antigravity%20IDE/resources/app/extensions/theme-symbols/src/icons/files/python.svg"/>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="1514475"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1026" name="AutoShape 2" descr="vscode-file://vscode-app/c:/Users/user/AppData/Local/Programs/Antigravity%20IDE/resources/app/extensions/theme-symbols/src/icons/files/python.svg"/>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="1933575"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1404,22 +2696,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:6">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="9"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
+      <c r="A3" s="20"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
     </row>
     <row r="5" spans="1:6" ht="30" customHeight="1">
       <c r="A5" s="1" t="s">
@@ -1722,28 +3014,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17.25" thickBot="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="8" t="s">
         <v>72</v>
       </c>
     </row>
@@ -1754,108 +3046,108 @@
       <c r="B2" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="D2" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="H2" s="10" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="22"/>
       <c r="B3" s="25"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
     </row>
     <row r="4" spans="1:8" ht="44.25">
       <c r="A4" s="22"/>
       <c r="B4" s="25"/>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="E4" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="G4" s="18" t="s">
+      <c r="G4" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="H4" s="18" t="s">
+      <c r="H4" s="16" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="22"/>
       <c r="B5" s="25"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="22"/>
       <c r="B6" s="25"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="14" t="s">
+      <c r="C6" s="11"/>
+      <c r="D6" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="F6" s="13"/>
-      <c r="G6" s="18" t="s">
+      <c r="F6" s="11"/>
+      <c r="G6" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="H6" s="18" t="s">
+      <c r="H6" s="16" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="22"/>
       <c r="B7" s="25"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
     </row>
     <row r="8" spans="1:8" ht="17.25" thickBot="1">
       <c r="A8" s="23"/>
       <c r="B8" s="26"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="17" t="s">
+      <c r="C8" s="13"/>
+      <c r="D8" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="19" t="s">
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="H8" s="15"/>
+      <c r="H8" s="13"/>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="21">
@@ -1864,106 +3156,106 @@
       <c r="B9" s="24" t="s">
         <v>91</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="G9" s="12" t="s">
+      <c r="G9" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="H9" s="12" t="s">
+      <c r="H9" s="10" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="22"/>
       <c r="B10" s="25"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
     </row>
     <row r="11" spans="1:8" ht="44.25">
       <c r="A11" s="22"/>
       <c r="B11" s="25"/>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="D11" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="E11" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="F11" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="G11" s="18" t="s">
+      <c r="G11" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="H11" s="18" t="s">
+      <c r="H11" s="16" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="22"/>
       <c r="B12" s="25"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="22"/>
       <c r="B13" s="25"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="14" t="s">
+      <c r="C13" s="11"/>
+      <c r="D13" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="E13" s="18" t="s">
+      <c r="E13" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="F13" s="14" t="s">
+      <c r="F13" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="22"/>
       <c r="B14" s="25"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
     </row>
     <row r="15" spans="1:8" ht="17.25" thickBot="1">
       <c r="A15" s="23"/>
       <c r="B15" s="26"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="17" t="s">
+      <c r="C15" s="13"/>
+      <c r="D15" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="E15" s="19" t="s">
+      <c r="E15" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="21">
@@ -1972,104 +3264,104 @@
       <c r="B16" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="E16" s="12" t="s">
+      <c r="E16" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="F16" s="12" t="s">
+      <c r="F16" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="G16" s="12" t="s">
+      <c r="G16" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="H16" s="12" t="s">
+      <c r="H16" s="10" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="22"/>
       <c r="B17" s="25"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
     </row>
     <row r="18" spans="1:8" ht="44.25">
       <c r="A18" s="22"/>
       <c r="B18" s="25"/>
-      <c r="C18" s="14" t="s">
+      <c r="C18" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="D18" s="14" t="s">
+      <c r="D18" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="E18" s="18" t="s">
+      <c r="E18" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="F18" s="14" t="s">
+      <c r="F18" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="G18" s="18" t="s">
+      <c r="G18" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="H18" s="18" t="s">
+      <c r="H18" s="16" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="22"/>
       <c r="B19" s="25"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="22"/>
       <c r="B20" s="25"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="14" t="s">
+      <c r="C20" s="11"/>
+      <c r="D20" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="E20" s="18" t="s">
+      <c r="E20" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="F20" s="14" t="s">
+      <c r="F20" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="22"/>
       <c r="B21" s="25"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11"/>
     </row>
     <row r="22" spans="1:8" ht="17.25" thickBot="1">
       <c r="A22" s="23"/>
       <c r="B22" s="26"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="19" t="s">
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="15"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="21">
@@ -2078,108 +3370,108 @@
       <c r="B23" s="24" t="s">
         <v>113</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C23" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="D23" s="16" t="s">
+      <c r="D23" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="E23" s="12" t="s">
+      <c r="E23" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="F23" s="12" t="s">
+      <c r="F23" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="G23" s="12" t="s">
+      <c r="G23" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="H23" s="12" t="s">
+      <c r="H23" s="10" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="22"/>
       <c r="B24" s="25"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
     </row>
     <row r="25" spans="1:8" ht="44.25">
       <c r="A25" s="22"/>
       <c r="B25" s="25"/>
-      <c r="C25" s="18" t="s">
+      <c r="C25" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="D25" s="14" t="s">
+      <c r="D25" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="E25" s="18" t="s">
+      <c r="E25" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="F25" s="14" t="s">
+      <c r="F25" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="G25" s="18" t="s">
+      <c r="G25" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="H25" s="18" t="s">
+      <c r="H25" s="16" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="22"/>
       <c r="B26" s="25"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="22"/>
       <c r="B27" s="25"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="14" t="s">
+      <c r="C27" s="11"/>
+      <c r="D27" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="E27" s="18" t="s">
+      <c r="E27" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="F27" s="14" t="s">
+      <c r="F27" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="G27" s="18" t="s">
+      <c r="G27" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="H27" s="18" t="s">
+      <c r="H27" s="16" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="22"/>
       <c r="B28" s="25"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
     </row>
     <row r="29" spans="1:8" ht="17.25" thickBot="1">
       <c r="A29" s="23"/>
       <c r="B29" s="26"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="19" t="s">
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
-      <c r="H29" s="15"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="13"/>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="21">
@@ -2188,19 +3480,19 @@
       <c r="B30" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="C30" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="D30" s="16" t="s">
+      <c r="D30" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="E30" s="12" t="s">
+      <c r="E30" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="F30" s="12" t="s">
+      <c r="F30" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="G30" s="12" t="s">
+      <c r="G30" s="10" t="s">
         <v>130</v>
       </c>
       <c r="H30" s="24" t="s">
@@ -2210,29 +3502,29 @@
     <row r="31" spans="1:8">
       <c r="A31" s="22"/>
       <c r="B31" s="25"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
-      <c r="G31" s="13"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
       <c r="H31" s="25"/>
     </row>
     <row r="32" spans="1:8" ht="44.25">
       <c r="A32" s="22"/>
       <c r="B32" s="25"/>
-      <c r="C32" s="18" t="s">
+      <c r="C32" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="D32" s="14" t="s">
+      <c r="D32" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="E32" s="18" t="s">
+      <c r="E32" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="F32" s="14" t="s">
+      <c r="F32" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="G32" s="18" t="s">
+      <c r="G32" s="16" t="s">
         <v>131</v>
       </c>
       <c r="H32" s="25"/>
@@ -2240,49 +3532,49 @@
     <row r="33" spans="1:8">
       <c r="A33" s="22"/>
       <c r="B33" s="25"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="13"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
       <c r="H33" s="25"/>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="22"/>
       <c r="B34" s="25"/>
-      <c r="C34" s="13"/>
-      <c r="D34" s="14" t="s">
+      <c r="C34" s="11"/>
+      <c r="D34" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="E34" s="18" t="s">
+      <c r="E34" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="F34" s="14" t="s">
+      <c r="F34" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="G34" s="13"/>
+      <c r="G34" s="11"/>
       <c r="H34" s="25"/>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="22"/>
       <c r="B35" s="25"/>
-      <c r="C35" s="13"/>
-      <c r="D35" s="13"/>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="13"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="11"/>
       <c r="H35" s="25"/>
     </row>
     <row r="36" spans="1:8" ht="17.25" thickBot="1">
       <c r="A36" s="23"/>
       <c r="B36" s="26"/>
-      <c r="C36" s="15"/>
-      <c r="D36" s="15"/>
-      <c r="E36" s="19" t="s">
+      <c r="C36" s="13"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="F36" s="15"/>
-      <c r="G36" s="15"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="13"/>
       <c r="H36" s="26"/>
     </row>
     <row r="37" spans="1:8">
@@ -2292,19 +3584,19 @@
       <c r="B37" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="C37" s="11" t="s">
+      <c r="C37" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="D37" s="16" t="s">
+      <c r="D37" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="E37" s="12" t="s">
+      <c r="E37" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="F37" s="12" t="s">
+      <c r="F37" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="G37" s="12" t="s">
+      <c r="G37" s="10" t="s">
         <v>139</v>
       </c>
       <c r="H37" s="24" t="s">
@@ -2314,29 +3606,29 @@
     <row r="38" spans="1:8">
       <c r="A38" s="22"/>
       <c r="B38" s="25"/>
-      <c r="C38" s="13"/>
-      <c r="D38" s="13"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="13"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
+      <c r="F38" s="11"/>
+      <c r="G38" s="11"/>
       <c r="H38" s="25"/>
     </row>
     <row r="39" spans="1:8" ht="44.25">
       <c r="A39" s="22"/>
       <c r="B39" s="25"/>
-      <c r="C39" s="18" t="s">
+      <c r="C39" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="D39" s="14" t="s">
+      <c r="D39" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="E39" s="18" t="s">
+      <c r="E39" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="F39" s="14" t="s">
+      <c r="F39" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="G39" s="18" t="s">
+      <c r="G39" s="16" t="s">
         <v>140</v>
       </c>
       <c r="H39" s="25"/>
@@ -2344,27 +3636,27 @@
     <row r="40" spans="1:8">
       <c r="A40" s="22"/>
       <c r="B40" s="25"/>
-      <c r="C40" s="13"/>
-      <c r="D40" s="13"/>
-      <c r="E40" s="13"/>
-      <c r="F40" s="13"/>
-      <c r="G40" s="13"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="11"/>
+      <c r="G40" s="11"/>
       <c r="H40" s="25"/>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="22"/>
       <c r="B41" s="25"/>
-      <c r="C41" s="13"/>
-      <c r="D41" s="14" t="s">
+      <c r="C41" s="11"/>
+      <c r="D41" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="E41" s="18" t="s">
+      <c r="E41" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="F41" s="14" t="s">
+      <c r="F41" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="G41" s="18" t="s">
+      <c r="G41" s="16" t="s">
         <v>141</v>
       </c>
       <c r="H41" s="25"/>
@@ -2372,23 +3664,23 @@
     <row r="42" spans="1:8">
       <c r="A42" s="22"/>
       <c r="B42" s="25"/>
-      <c r="C42" s="13"/>
-      <c r="D42" s="13"/>
-      <c r="E42" s="13"/>
-      <c r="F42" s="13"/>
-      <c r="G42" s="13"/>
+      <c r="C42" s="11"/>
+      <c r="D42" s="11"/>
+      <c r="E42" s="11"/>
+      <c r="F42" s="11"/>
+      <c r="G42" s="11"/>
       <c r="H42" s="25"/>
     </row>
     <row r="43" spans="1:8" ht="17.25" thickBot="1">
       <c r="A43" s="23"/>
       <c r="B43" s="26"/>
-      <c r="C43" s="15"/>
-      <c r="D43" s="15"/>
-      <c r="E43" s="19" t="s">
+      <c r="C43" s="13"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="F43" s="15"/>
-      <c r="G43" s="15"/>
+      <c r="F43" s="13"/>
+      <c r="G43" s="13"/>
       <c r="H43" s="26"/>
     </row>
     <row r="44" spans="1:8">
@@ -2398,108 +3690,108 @@
       <c r="B44" s="24" t="s">
         <v>143</v>
       </c>
-      <c r="C44" s="11" t="s">
+      <c r="C44" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="D44" s="16" t="s">
+      <c r="D44" s="14" t="s">
         <v>146</v>
       </c>
-      <c r="E44" s="12" t="s">
+      <c r="E44" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="F44" s="12" t="s">
+      <c r="F44" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="G44" s="12" t="s">
+      <c r="G44" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="H44" s="12" t="s">
+      <c r="H44" s="10" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="22"/>
       <c r="B45" s="25"/>
-      <c r="C45" s="13"/>
-      <c r="D45" s="13"/>
-      <c r="E45" s="13"/>
-      <c r="F45" s="13"/>
-      <c r="G45" s="13"/>
-      <c r="H45" s="13"/>
+      <c r="C45" s="11"/>
+      <c r="D45" s="11"/>
+      <c r="E45" s="11"/>
+      <c r="F45" s="11"/>
+      <c r="G45" s="11"/>
+      <c r="H45" s="11"/>
     </row>
     <row r="46" spans="1:8" ht="44.25">
       <c r="A46" s="22"/>
       <c r="B46" s="25"/>
-      <c r="C46" s="14" t="s">
+      <c r="C46" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="D46" s="14" t="s">
+      <c r="D46" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="E46" s="18" t="s">
+      <c r="E46" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="F46" s="14" t="s">
+      <c r="F46" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="G46" s="18" t="s">
+      <c r="G46" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="H46" s="18" t="s">
+      <c r="H46" s="16" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="22"/>
       <c r="B47" s="25"/>
-      <c r="C47" s="13"/>
-      <c r="D47" s="13"/>
-      <c r="E47" s="13"/>
-      <c r="F47" s="13"/>
-      <c r="G47" s="13"/>
-      <c r="H47" s="13"/>
+      <c r="C47" s="11"/>
+      <c r="D47" s="11"/>
+      <c r="E47" s="11"/>
+      <c r="F47" s="11"/>
+      <c r="G47" s="11"/>
+      <c r="H47" s="11"/>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="22"/>
       <c r="B48" s="25"/>
-      <c r="C48" s="13"/>
-      <c r="D48" s="14" t="s">
+      <c r="C48" s="11"/>
+      <c r="D48" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="E48" s="18" t="s">
+      <c r="E48" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="F48" s="14" t="s">
+      <c r="F48" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="G48" s="18" t="s">
+      <c r="G48" s="16" t="s">
         <v>152</v>
       </c>
-      <c r="H48" s="13"/>
+      <c r="H48" s="11"/>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="22"/>
       <c r="B49" s="25"/>
-      <c r="C49" s="13"/>
-      <c r="D49" s="13"/>
-      <c r="E49" s="13"/>
-      <c r="F49" s="13"/>
-      <c r="G49" s="13"/>
-      <c r="H49" s="13"/>
+      <c r="C49" s="11"/>
+      <c r="D49" s="11"/>
+      <c r="E49" s="11"/>
+      <c r="F49" s="11"/>
+      <c r="G49" s="11"/>
+      <c r="H49" s="11"/>
     </row>
     <row r="50" spans="1:8" ht="17.25" thickBot="1">
       <c r="A50" s="23"/>
       <c r="B50" s="26"/>
-      <c r="C50" s="15"/>
-      <c r="D50" s="17" t="s">
+      <c r="C50" s="13"/>
+      <c r="D50" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="E50" s="19" t="s">
+      <c r="E50" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="F50" s="15"/>
-      <c r="G50" s="15"/>
-      <c r="H50" s="15"/>
+      <c r="F50" s="13"/>
+      <c r="G50" s="13"/>
+      <c r="H50" s="13"/>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="21">
@@ -2508,119 +3800,111 @@
       <c r="B51" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="C51" s="11" t="s">
+      <c r="C51" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="D51" s="16" t="s">
+      <c r="D51" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="E51" s="12" t="s">
+      <c r="E51" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="F51" s="12" t="s">
+      <c r="F51" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="G51" s="12" t="s">
+      <c r="G51" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="H51" s="16" t="s">
+      <c r="H51" s="14" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="22"/>
       <c r="B52" s="25"/>
-      <c r="C52" s="13"/>
-      <c r="D52" s="13"/>
-      <c r="E52" s="13"/>
-      <c r="F52" s="13"/>
-      <c r="G52" s="13"/>
-      <c r="H52" s="13"/>
+      <c r="C52" s="11"/>
+      <c r="D52" s="11"/>
+      <c r="E52" s="11"/>
+      <c r="F52" s="11"/>
+      <c r="G52" s="11"/>
+      <c r="H52" s="11"/>
     </row>
     <row r="53" spans="1:8" ht="44.25">
       <c r="A53" s="22"/>
       <c r="B53" s="25"/>
-      <c r="C53" s="14" t="s">
+      <c r="C53" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="D53" s="14" t="s">
+      <c r="D53" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="E53" s="18" t="s">
+      <c r="E53" s="16" t="s">
         <v>161</v>
       </c>
-      <c r="F53" s="20" t="s">
+      <c r="F53" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="G53" s="18" t="s">
+      <c r="G53" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="H53" s="14" t="s">
+      <c r="H53" s="12" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="22"/>
       <c r="B54" s="25"/>
-      <c r="C54" s="13"/>
-      <c r="D54" s="13"/>
-      <c r="E54" s="13"/>
-      <c r="F54" s="13"/>
-      <c r="G54" s="13"/>
-      <c r="H54" s="13"/>
+      <c r="C54" s="11"/>
+      <c r="D54" s="11"/>
+      <c r="E54" s="11"/>
+      <c r="F54" s="11"/>
+      <c r="G54" s="11"/>
+      <c r="H54" s="11"/>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="22"/>
       <c r="B55" s="25"/>
-      <c r="C55" s="13"/>
-      <c r="D55" s="14" t="s">
+      <c r="C55" s="11"/>
+      <c r="D55" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="E55" s="18" t="s">
+      <c r="E55" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="F55" s="14" t="s">
+      <c r="F55" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="G55" s="18" t="s">
+      <c r="G55" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="H55" s="13"/>
+      <c r="H55" s="11"/>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="22"/>
       <c r="B56" s="25"/>
-      <c r="C56" s="13"/>
-      <c r="D56" s="13"/>
-      <c r="E56" s="13"/>
-      <c r="F56" s="13"/>
-      <c r="G56" s="13"/>
-      <c r="H56" s="13"/>
+      <c r="C56" s="11"/>
+      <c r="D56" s="11"/>
+      <c r="E56" s="11"/>
+      <c r="F56" s="11"/>
+      <c r="G56" s="11"/>
+      <c r="H56" s="11"/>
     </row>
     <row r="57" spans="1:8" ht="17.25" thickBot="1">
       <c r="A57" s="23"/>
       <c r="B57" s="26"/>
-      <c r="C57" s="15"/>
-      <c r="D57" s="17" t="s">
+      <c r="C57" s="13"/>
+      <c r="D57" s="15" t="s">
         <v>160</v>
       </c>
-      <c r="E57" s="19" t="s">
+      <c r="E57" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="F57" s="15"/>
-      <c r="G57" s="15"/>
-      <c r="H57" s="15"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A44:A50"/>
-    <mergeCell ref="B44:B50"/>
-    <mergeCell ref="A51:A57"/>
-    <mergeCell ref="B51:B57"/>
-    <mergeCell ref="A23:A29"/>
-    <mergeCell ref="B23:B29"/>
-    <mergeCell ref="A30:A36"/>
-    <mergeCell ref="B30:B36"/>
     <mergeCell ref="H30:H36"/>
     <mergeCell ref="A37:A43"/>
     <mergeCell ref="B37:B43"/>
@@ -2631,8 +3915,361 @@
     <mergeCell ref="B9:B15"/>
     <mergeCell ref="A16:A22"/>
     <mergeCell ref="B16:B22"/>
+    <mergeCell ref="A44:A50"/>
+    <mergeCell ref="B44:B50"/>
+    <mergeCell ref="A51:A57"/>
+    <mergeCell ref="B51:B57"/>
+    <mergeCell ref="A23:A29"/>
+    <mergeCell ref="B23:B29"/>
+    <mergeCell ref="A30:A36"/>
+    <mergeCell ref="B30:B36"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C68"/>
+  <sheetFormatPr defaultColWidth="74.125" defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="2" width="74.125" style="34"/>
+    <col min="3" max="16384" width="74.125" style="27"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="43.5">
+      <c r="A1" s="33" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="33" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="33" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="33"/>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="33" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="33"/>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="33" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="35"/>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="35"/>
+    </row>
+    <row r="11" spans="1:1" ht="112.5">
+      <c r="A11" s="36" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="35"/>
+    </row>
+    <row r="13" spans="1:1" ht="43.5">
+      <c r="A13" s="33" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="35"/>
+    </row>
+    <row r="16" spans="1:1" ht="27" thickBot="1">
+      <c r="A16" s="37" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="17.25" thickBot="1">
+      <c r="A17" s="38"/>
+    </row>
+    <row r="18" spans="1:3" ht="17.25" thickBot="1">
+      <c r="A18" s="39" t="s">
+        <v>175</v>
+      </c>
+      <c r="B18" s="40" t="s">
+        <v>176</v>
+      </c>
+      <c r="C18" s="28" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="17.25" thickBot="1">
+      <c r="A19" s="41" t="s">
+        <v>195</v>
+      </c>
+      <c r="B19" s="42" t="s">
+        <v>178</v>
+      </c>
+      <c r="C19" s="29" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="17.25" thickBot="1">
+      <c r="A20" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="B20" s="42" t="s">
+        <v>196</v>
+      </c>
+      <c r="C20" s="30" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="17.25" thickBot="1">
+      <c r="A21" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="B21" s="44" t="s">
+        <v>198</v>
+      </c>
+      <c r="C21" s="31" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="17.25" thickBot="1">
+      <c r="A22" s="43" t="s">
+        <v>182</v>
+      </c>
+      <c r="B22" s="42" t="s">
+        <v>183</v>
+      </c>
+      <c r="C22" s="29" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="17.25" thickBot="1">
+      <c r="A23" s="43" t="s">
+        <v>184</v>
+      </c>
+      <c r="B23" s="44" t="s">
+        <v>201</v>
+      </c>
+      <c r="C23" s="29" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="45" t="s">
+        <v>185</v>
+      </c>
+      <c r="B24" s="46" t="s">
+        <v>186</v>
+      </c>
+      <c r="C24" s="32" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="35"/>
+    </row>
+    <row r="27" spans="1:3" ht="26.25">
+      <c r="A27" s="37" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="35"/>
+    </row>
+    <row r="29" spans="1:3" ht="21">
+      <c r="A29" s="47" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="48"/>
+    </row>
+    <row r="31" spans="1:3" ht="29.25">
+      <c r="A31" s="49" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="50" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="51" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="51" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" ht="29.25">
+      <c r="A35" s="52" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="35"/>
+    </row>
+    <row r="37" spans="1:1" ht="42">
+      <c r="A37" s="47" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="48"/>
+    </row>
+    <row r="39" spans="1:1" ht="29.25">
+      <c r="A39" s="49" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="49" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="53" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" ht="29.25">
+      <c r="A42" s="53" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" ht="29.25">
+      <c r="A43" s="53" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="52"/>
+    </row>
+    <row r="45" spans="1:1" ht="29.25">
+      <c r="A45" s="54" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="35"/>
+    </row>
+    <row r="47" spans="1:1" ht="21">
+      <c r="A47" s="47" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="35"/>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" s="55" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" s="48"/>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" s="56" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" s="56" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="56" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="35"/>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" s="35"/>
+    </row>
+    <row r="57" spans="1:2" ht="26.25">
+      <c r="A57" s="37" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" s="48"/>
+    </row>
+    <row r="59" spans="1:2" ht="29.25">
+      <c r="A59" s="56" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" ht="29.25">
+      <c r="A60" s="56" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" ht="29.25">
+      <c r="A61" s="56" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" s="57" t="s">
+        <v>229</v>
+      </c>
+      <c r="B64" s="57" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" s="57" t="s">
+        <v>221</v>
+      </c>
+      <c r="B65" s="57" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" s="57" t="s">
+        <v>224</v>
+      </c>
+      <c r="B66" s="57" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" s="57" t="s">
+        <v>223</v>
+      </c>
+      <c r="B67" s="57" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" s="57" t="s">
+        <v>227</v>
+      </c>
+      <c r="B68" s="57" t="s">
+        <v>228</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>